--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_004/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_cht_004/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -359,21 +364,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -530,46 +520,6 @@
       </text>
     </comment>
     <comment ref="I6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="A7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="E7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="F7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="H7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="I7" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1321,7 +1271,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Cold Plate CHT Model — MTRX-500 Power Module</t>
+          <t>Cold Plate CHT Model — MTRX-500 Power Module Node-3 Avionics Rack</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1331,7 +1281,7 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Steady-state conjugate heat transfer (CHT) model of an aluminum/copper cold plate assembly cooling a 6-die MTRX-500 power module in the Node-3 avionics rack. The model predicts Tj,max and coolant pressure drop under nominal operating conditions (inlet 20 ± 0.6 C, flow 0.12 ± 0.004 kg/s, 540 W total heat). Used to assess compliance with the PSB-2 pass/fail rule: Tj,max ≤ 85 C.</t>
+          <t>Steady-state conjugate heat transfer (CHT) simulation of an aluminum/copper cold plate for the MTRX-500 power module in the Node-3 avionics rack. The model predicts Tj,max and coolant pressure drop under nominal and off-nominal thermal-hydraulic conditions to support a pass/fail decision at the PSB-2 design gate (Tj,max ≤ 85 C at inlet 20 ± 0.6 C, flow 0.12 ± 0.004 kg/s, 540 W total heat).</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1346,12 +1296,12 @@
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>MRL 3</t>
+          <t>MRL 4</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
@@ -1369,9 +1319,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md (Cold Plate CHT credibility status memo, J. Kim / D. Ortega / S. Patel, 06 Aug 2026)</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1432,7 +1382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1490,7 +1440,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>PSB-2 Thermal Pass/Fail Rule</t>
+          <t>PSB-2 Thermal Pass/Fail Criterion</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1500,7 +1450,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Tj,max ≤ 85 C at inlet 20 ± 0.6 C, flow 0.12 ± 0.004 kg/s, and 540 W total heat; exceedance probability must be acceptably low under specified input uncertainty distributions.</t>
+          <t>Tj,max ≤ 85 C at inlet 20 ± 0.6 C, flow 0.12 ± 0.004 kg/s, and 540 W total heat dissipation; coolant pressure drop must also be predicted to support subsystem trades</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1522,12 +1472,12 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>Cold Plate CHT Model (STAR-CCM+ 2023.3, coldplate-cht_v1.7)</t>
+          <t>STAR-CCM+ 2023.3 CHT Model (coldplate-cht_v1.7)</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Full conjugate heat transfer model (RANS k-omega SST, low-Re, y+&lt;1) of the aluminum 6061-T6 baseplate, copper spreader, TIM layers, stainless fittings, and 50/50 water-glycol coolant; steady-state, no boiling, radiation neglected.</t>
+          <t>Full conjugate heat transfer RANS (k-ω SST, low-Re, y+ &lt; 1) model of the 6-die MTRX-500 cold plate; aluminum 6061-T6 baseplate, copper spreader, TIM layers, stainless fittings, 50/50 water-glycol coolant with temperature-dependent properties</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1494,7 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Three steady-state hardware tests at 0.12 kg/s, 540 W with 26 thermocouples and IR camera; additional off-nominal point at 0.10 kg/s; NIST-traceable instrumentation with documented uncertainties.</t>
+          <t>Measurements from purpose-built fixture at GRC Thermal Lab: 26 thermocouples on die caps and cold plate, FLIR A655sc IR camera; three steady-state runs at 0.12 kg/s / 540 W nominal and one off-nominal point at 0.10 kg/s; pressure drop measurements at both conditions</t>
         </is>
       </c>
     </row>
@@ -1556,29 +1506,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>TIM and Contact Resistance Characterization Data</t>
+          <t>Material and Boundary Condition Characterization Data</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Laser-flash thermal conductivity measurements (mean 3.4 W/m-K, COV 18%) and coupon-level contact resistance measurements (Rc = 1.1e-4 m2-K/W ± 30%) used as model inputs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>Latin Hypercube UQ Sampling Dataset</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>200-point Latin hypercube propagation over six uncertain inputs (flow, inlet T, TIM k, Rc, heat split, turbulence intensity) yielding 95% interval [81.9, 86.1] C for Tj,max and Sobol sensitivity indices.</t>
+          <t>TIM thermal conductivity from laser flash analysis (mean 3.4 W/m-K, COV 18%); contact resistance from coupon test (Rc = 1.1e-4 m2-K/W ± 30%); heater map from electrical spec validated by bench measurements (±2%); flow and temperature from JSC Thermal Loop spec with calibrated Micro Motion CMF025 and NIST-traceable Type-T thermocouples</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2015,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Nominal Condition Temperature and Pressure Drop Comparison</t>
+          <t>Nominal Validation — Junction Temperature and Pressure Drop</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2030,12 +1963,12 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Model predictions compared to average of three steady hardware tests at 0.12 kg/s, 540 W, 20 C inlet on purpose-built GRC Thermal Lab fixture with identical flow path and stack-up.</t>
+          <t>Model predictions compared against three replicate steady-state hardware tests at 0.12 kg/s, 540 W, ~20 C inlet using 26 thermocouples and IR camera. Model Tj,max = 83.7 C vs test mean 81.9 C (σ = 0.5 C); bias +1.8 C; RMSE across all sensors 2.1 C. Pressure drop: model 25.9 kPa vs test 24.6 kPa (+5.3%).</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Hardware test mean Tj,max,test = 81.9 C (σ = 0.5 C); pressure drop test = 24.6 kPa</t>
+          <t>GRC Thermal Lab hardware measurements (three replicates)</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
@@ -2045,24 +1978,24 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Experimental repeatability (σ = 0.5 C); numerical GCI-style estimate for Tj,max = 1.8%</t>
+          <t>Test repeatability (σ = 0.5 C); 200-point Latin hypercube propagation covering flow ±3%, inlet T ±0.6 C, TIM k ±20%, Rc ±30%, heat split ±10%, turbulence intensity 1–5%, plus mesh-study variance; 95% interval [81.9, 86.1] C; Sobol sensitivity indices</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>Tj,max bias = +1.8 C; RMSE across all sensors = 2.1 C; pressure drop bias = +5.3%</t>
+          <t>Bias +1.8 C (Tj,max); RMSE 2.1 C; pressure drop bias +5.3%; 95% CI [81.9, 86.1] C; exceedance probability P(Tj &gt; 85 C) = 0.28 at nominal spec</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Inconclusive</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Off-Nominal Flow Condition Cross-Check</t>
+          <t>Off-Nominal Validation — Reduced Flow (0.10 kg/s)</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2072,12 +2005,12 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Model compared to hardware data at off-nominal 0.10 kg/s to assess prediction quality outside the nominal operating point; pre-set acceptance band ±5 C.</t>
+          <t>Cross-check at off-nominal flow condition 0.10 kg/s; model bias increases to +2.6 C relative to hardware, within pre-set ±5 C acceptance band. Validates model trend across flow range.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>Hardware test at 0.10 kg/s</t>
+          <t>GRC Thermal Lab hardware measurement at 0.10 kg/s</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
@@ -2087,7 +2020,7 @@
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>Bias = +2.6 C (within ±5 C pre-set acceptance band)</t>
+          <t>Bias +2.6 C; within ±5 C acceptance band</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2099,7 +2032,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study (GCI)</t>
+          <t>Mesh Convergence / Discretization Study</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2109,12 +2042,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Three systematically refined meshes (4.2M, 8.6M, 17.3M cells) evaluated for Tj,max convergence; GCI-style discretization error estimate computed.</t>
+          <t>Three-mesh refinement study (4.2M, 8.6M, 17.3M cells). Max die-surface temperature change M1→M2: 1.6 C; M2→M3: 0.5 C. GCI-style estimate for Tj,max = 1.8%. Monotonic convergence confirmed.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolation / GCI framework</t>
+          <t>Richardson extrapolation / GCI methodology</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2124,12 +2057,12 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>GCI-style Richardson extrapolation</t>
+          <t>Grid Convergence Index (GCI-style Richardson extrapolation)</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>M1→M2 change = 1.6 C; M2→M3 change = 0.5 C; GCI for Tj,max = 1.8%</t>
+          <t>GCI for Tj,max = 1.8%; M2→M3 change 0.5 C</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2141,7 +2074,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Iterative Solver Convergence and Mass/Energy Balance Check</t>
+          <t>Code Regression and Manufactured Solutions Verification</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2151,12 +2084,12 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Iterative residuals monitored to convergence threshold; global mass and energy balances verified; energy closure criterion enforced in CI.</t>
+          <t>Weekly regression suite of 15 cases including manufactured solutions for heat conduction and lid-driven cavity benchmark; no deltas recorded this quarter. Confirms solver correctness at STAR-CCM+ 2023.3.1 patch level.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Prescribed targets: residuals &lt; 1e-6; mass balance &lt; 0.1%; energy balance 98–101%; energy closure enforced in CI</t>
+          <t>Analytical/manufactured solutions and established benchmark results</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
@@ -2166,54 +2099,12 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Residuals &lt; 1e-6; mass balance 0.1%; energy balance 1.2%; closure 98–101%</t>
+          <t>Zero regressions this quarter; 15-case suite passing</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>UQ Propagation and Exceedance Probability Assessment</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>ValidationResult</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>200-point Latin hypercube sampling propagated six uncertain inputs through the CHT model; Sobol first-order sensitivity indices computed; 95% interval and exceedance probability for Tj,max ≤ 85 C reported.</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>PSB-2 limit of 85 C</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>Latin hypercube sampling (200 points), Sobol sensitivity analysis</t>
-        </is>
-      </c>
-      <c r="H7" s="13" t="inlineStr">
-        <is>
-          <t>95% interval [81.9, 86.1] C; exceedance probability P(Tj,max &gt; 85 C) = 0.28 at nominal spec; drops below 0.05 with TIM upgrade</t>
-        </is>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -2355,19 +2246,19 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Software has documented regression testing, version control, and reproducibility across compute platforms.</t>
+          <t>Commercial solver with documented QA processes, regression testing, version control, and frozen deployment environment</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>STAR-CCM+ 2023.3.1 used in double precision with license and solver patch level frozen. Weekly regression suite (15 cases) includes manufactured solutions for heat conduction and lid-driven cavity with no deltas this quarter. Git LFS repository tag coldplate-cht_v1.7 archives all meshes, journals, and reports. Runs are bitwise repeatable on two distinct HPC platforms within 0.2 C (non-bitwise variation attributed to BLAS). Apptainer containers pin OS and libraries with SHA256 image hashes recorded. Post-processing scripts include automated unit checks and a residual sanity gate enforced in CI.</t>
+          <t>STAR-CCM+ 2023.3.1 (commercial solver) deployed via Apptainer containers with SHA256-recorded images, freezing OS and library stack. Weekly 15-case regression suite with manufactured solutions shows zero deltas this quarter. Git LFS repository (tag coldplate-cht_v1.7) archives all meshes, journals, and reports. License and solver patch level frozen. Bitwise reproducibility confirmed across two HPC clusters within 0.2 C (non-bitwise tolerance due to BLAS). SQA co-authored by S. Patel. CI enforces energy closure criterion 98–101%.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2389,19 +2280,19 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Code correctness demonstrated via comparison to analytical or manufactured solutions for relevant physics.</t>
+          <t>Code correctly solves governing equations, demonstrated via manufactured solutions or established benchmarks</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Weekly regression suite explicitly includes manufactured solutions for heat conduction and lid-driven cavity flow, directly relevant to the CHT physics. No regression deltas reported this quarter. These serve as ongoing MMS/benchmark verification of the governing-equation solver implementation in STAR-CCM+.</t>
+          <t>Weekly regression suite includes manufactured solutions for heat conduction and lid-driven cavity benchmark. No regressions observed this quarter. These checks provide direct evidence that the solver correctly implements the governing energy and Navier-Stokes equations within the deployed version.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2423,19 +2314,19 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh convergence demonstrated with quantified GCI or equivalent; solution on finest practical mesh used for validation comparisons.</t>
+          <t>Mesh convergence demonstrated with quantified GCI or equivalent; discretization error bounded and included in UQ</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three systematically refined meshes (4.2M, 8.6M, 17.3M cells; refinement ratio ~2x) were run. Tj,max changes: M1→M2 = 1.6 C, M2→M3 = 0.5 C, indicating monotonic convergence. GCI-style estimate for Tj,max = 1.8%. Numerical spread from mesh study incorporated as fixed additive variance in the UQ. y+ &lt; 1 enforced at all wetted walls.</t>
+          <t>Three-mesh refinement study (4.2M → 8.6M → 17.3M cells) with monotonic convergence. Tj,max change M2→M3 = 0.5 C; GCI-style estimate = 1.8% for Tj,max. Mesh-study variance included as a fixed additive term in the 200-point LHS UQ propagation, ensuring discretization uncertainty propagates to the 95% output interval.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2457,19 +2348,19 @@
         </is>
       </c>
       <c r="C8" s="14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Iterative residuals meet prescribed targets; global conservation balances verified.</t>
+          <t>Iterative residuals reach adequate targets; mass and energy balances verified</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Iterative residuals &lt; 1e-6 (all equations). Global mass balance within 0.1%, energy balance within 1.2%. Energy closure criterion 98–101% enforced as a CI gate on every run. Mass and energy balance metrics reported alongside solver settings locked in an environment module file.</t>
+          <t>Iterative residuals &lt; 1e-6 (all equations). Mass balance within 0.1%; energy balance within 1.2% (CI enforces 98–101% energy closure). Runs are bitwise repeatable on Pleiades ICX and confirmed within 0.2 C on EPYC cluster. Solver settings locked in environment module file.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2491,19 +2382,19 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent review of model setup, boundary conditions, units, and post-processing; pre-run checklist documented.</t>
+          <t>Independent review of model setup, boundary condition verification, units checks, and pre-run checklist</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Two-person rule applied for boundary conditions and units verification; pre-run checklist signed. Independent peer review by M. Rios (not on design team) and test lead D. Ortega. External independent review by TX40 Analysis Advisory Team on 18 Jul 2026; all action items (radiation check, Rc coupon) closed 01 Aug 2026. All artifacts linked to requirements in DOORS; checklist aligned with VVUQ plan dated 10 May. Post-processing scripts compare virtual sensor points to physical test locations with automated checks.</t>
+          <t>Two-person rule applied for boundary condition specification and unit verification. Pre-run checklist signed by analysts. Independent peer review by M. Rios (not on design team). External review by TX40 Analysis Advisory Team on 18 Jul 2026; action items (radiation check, Rc coupon) closed 01 Aug. Post-processing scripts compare virtual sensor points to test locations with automated unit checks and a residual sanity gate. All artifacts linked to requirements in DOORS.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2525,19 +2416,19 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and turbulence model selection justified for the flow regime; key simplifying assumptions documented with impact assessments.</t>
+          <t>Governing physics justified, turbulence model selection documented, known limitations stated</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>RANS k-omega SST with low-Re treatment and y+&lt;1 selected — appropriate for internal forced convection in the flow regime of interest. Steady-state assumption justified by time constants &gt; 300 s vs. steady decision criteria. No-boiling assumption justified by 2.3 bar(g) operating pressure and wall superheat margins &gt; 30 C. Radiation neglected based on enclosed rack geometry (view factors near zero) and spot check showing &lt; 0.4 C effect. Dittus-Boelter trend comparison at extrapolated inlet temperature confirms model physics at boundary of COU envelope. Limitations (no boiling model, radiation neglected at higher fluxes) documented explicitly.</t>
+          <t>RANS k-ω SST with low-Re treatment and y+ &lt; 1 selected and documented; appropriate for internal channel flows with modest adverse pressure gradients. Steady-state justified by time constants &gt; 300 s vs. steady design limits. No boiling expected: operating pressure 2.3 bar(g) with Ts−Tw,min &gt; 30 C margin. Radiation neglected with spot-check confirming &lt; 0.4 C effect. Limitations explicitly documented: no boiling model, radiation approximation. Dittus-Boelter cross-check at 18 C inlet confirms model trends within 3%.</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2559,19 +2450,19 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>Key material properties and boundary conditions characterized with quantified uncertainties from measurements or traceable sources.</t>
+          <t>Material properties from testing, boundary conditions from calibrated measurements, input uncertainties characterized</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>TIM conductivity measured via laser flash (mean 3.4 W/m-K, COV 18%). Contact resistance from coupon test (Rc = 1.1e-4 m2-K/W ± 30%). Heater map from electrical spec validated by bench electrical measurements (±2%). Inlet flow from JSC Thermal Loop spec; flowmeter is Micro Motion CMF025 (±0.5%). Inlet temperature from NIST-traceable Type T thermocouples (±0.3 C, 1σ). CAD from PDM Rev C with documented feature suppression decisions. All six major input uncertainties characterized and propagated in UQ.</t>
+          <t>TIM conductivity from laser flash analysis (mean 3.4 W/m-K, COV 18%). Contact resistance from coupon test (Rc = 1.1e-4 m2-K/W ± 30%). Heater map from electrical spec, validated by bench electrical measurements ± 2%. Inlet flow from JSC Thermal Loop spec; Micro Motion CMF025 flowmeter ± 0.5% of rate. NIST-traceable Type-T thermocouples ± 0.3 C (1σ). CAD from PDM Rev C with controlled geometry simplification. All input uncertainties quantified and carried into LHS UQ propagation.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2600,12 +2491,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article is production-representative; number of tests sufficient for statistical characterization.</t>
+          <t>Hardware representative of production configuration; adequate number of test articles characterized</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Purpose-built fixture at GRC Thermal Lab described as having identical flow path and fixture stack-up to the design hardware. Three repeated steady-state tests conducted at nominal conditions, yielding Tj,max,test = 81.9 C with σ = 0.5 C across repeats. One additional off-nominal test point at 0.10 kg/s. Number of specimens not explicitly discussed beyond repeatability of a single fixture; production-representativeness asserted but not independently verified with CMM or inspection data.</t>
+          <t>Purpose-built fixture at GRC Thermal Lab described as having identical flow path and fixture stack-up to the design configuration. Three replicate steady-state tests conducted at nominal conditions; one off-nominal point at 0.10 kg/s. No explicit documentation of sample production representativeness or formal sample-size justification, but fixture fidelity to the design is stated. Single test article used for all runs.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2627,19 +2518,19 @@
         </is>
       </c>
       <c r="C13" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Test conditions well-controlled and measured with calibrated, traceable instrumentation; measurement uncertainties documented.</t>
+          <t>Calibrated instrumentation, controlled environment, documented measurement uncertainty, traceable standards</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>26 thermocouples on die caps and cold plate; FLIR A655sc IR camera (emissivity painted 0.95 ± 0.02). Type T thermocouples NIST-traceable, ±0.3 C (1σ). Micro Motion CMF025 flowmeter ±0.5% of rate. Tests conducted at 0.12 kg/s and 540 W with three steady-state repeats. Off-nominal condition at 0.10 kg/s also executed. Inlet temperature range in tests 19.5–21.0 C (slightly narrower than full COU envelope of 18–22 C). Controlled steady-state conditions confirmed by repeatability.</t>
+          <t>26 thermocouples (Type T, NIST-traceable, ±0.3 C 1σ) on die caps and cold plate. FLIR A655sc IR camera (emissivity painted 0.95 ± 0.02). Micro Motion CMF025 flowmeter (±0.5% of rate). Three replicate steady-state runs with σ = 0.5 C repeatability for Tj,max. Inlet temperature and flow rate controlled and measured against JSC Thermal Loop spec. Measurement uncertainties explicitly documented and propagated.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2661,19 +2552,19 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model boundary conditions matched to measured test conditions; input uncertainties propagated to output comparison.</t>
+          <t>Model inputs matched to experimental conditions with uncertainty propagation; boundary condition correspondence documented</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Model run on matched sensor locations for comparison. Inlet flow (0.12 kg/s) and temperature (20 C) matched to test spec; flowmeter and thermocouple uncertainties documented. Heater power split validated by electrical measurements (±2%). All six uncertain inputs (flow ±3%, inlet T ±0.6 C, TIM k ±20%, Rc ±30%, heat split ±10%, turbulence intensity 1–5%) propagated via 200-point LHS including numerical spread from mesh study. Sobol indices identify dominant contributors. Post-processing scripts explicitly compare virtual sensor points to physical test locations.</t>
+          <t>Model boundary conditions set to match the test fixture: same flow rate (0.12 kg/s), inlet temperature (~20 C), heat load map (6-die split validated ±2%), and geometry (CAD Rev C matched to fixture). Virtual sensor locations in the model matched to physical thermocouple positions in post-processing scripts. Input uncertainties (flow ±3%, inlet T ±0.6 C, TIM k ±20%, Rc ±30%, heat split ±10%) propagated through 200-point LHS including measurement uncertainty sources.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2695,19 +2586,19 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison metrics (bias, RMSE) reported at multiple sensor locations; uncertainty bands included; pre-defined acceptance criteria applied.</t>
+          <t>Quantitative comparison metrics across multiple output quantities and sensor locations; uncertainty bands reported; statistical metrics computed</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Nominal comparison: Tj,max bias = +1.8 C; RMSE across all 26 sensors = 2.1 C; pressure drop bias = +5.3%. Off-nominal (0.10 kg/s): bias = +2.6 C, within pre-defined ±5 C acceptance band. 95% prediction interval [81.9, 86.1] C reported. Exceedance probability P(Tj,max &gt; 85 C) = 0.28 at nominal spec quantified. Pre-set acceptance band documented before testing. Comparison covers both temperature field (multi-sensor) and integrated pressure drop. IR camera provides spatial cross-check.</t>
+          <t>Tj,max bias = +1.8 C (model 83.7 C vs test mean 81.9 C, σ = 0.5 C). RMSE across all 26 sensor locations = 2.1 C. Pressure drop bias = +5.3% (25.9 kPa vs 24.6 kPa). Off-nominal cross-check at 0.10 kg/s: bias +2.6 C, within ±5 C acceptance band. 95% predictive interval [81.9, 86.1] C from LHS UQ. Sobol first-order sensitivity indices reported (TIM k: 0.41; flow: 0.37). Pre-defined acceptance band (±5 C) documented.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2729,19 +2620,19 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>Model QoIs directly correspond to the pass/fail decision criteria and are measurable both computationally and experimentally.</t>
+          <t>QoI directly addresses the safety/performance requirement and is measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Primary QoIs — Tj,max and coolant pressure drop — map directly to the PSB-2 pass/fail rule (Tj,max ≤ 85 C). Both QoIs are predicted by the CHT model and measured in the GRC hardware test (thermocouples/IR for temperature, pressure transducers for pressure drop). Sobol analysis further confirms TIM properties and flow rate as dominant drivers of the key QoI. Exceedance probability is computed directly for the decision threshold.</t>
+          <t>Tj,max is precisely the quantity specified in the PSB-2 pass/fail rule (≤ 85 C). Coolant pressure drop is a secondary QoI for subsystem trades. Both are computed in the model and directly measured in the validation fixture (thermocouples / IR camera for temperature; pressure transducers for drop). Sobol analysis quantifies which inputs drive Tj,max, supporting design trades. The exceedance probability P(Tj &gt; 85 C) = 0.28 directly maps to the decision criterion.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2763,19 +2654,19 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions cover the full intended use envelope for flow rate and inlet temperature; same geometry and physics regime.</t>
+          <t>Validation conditions cover the intended use envelope; gaps identified and assessed</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation geometry is identical to the COU hardware (same flow path and stack-up). Nominal COU flow (0.12 kg/s) and off-nominal (0.10 kg/s) are within the intended COU range of 0.10–0.14 kg/s, fully covered by the test matrix. Inlet temperature in tests (19.5–21.0 C) partially covers the COU envelope (18–22 C); the 18 C lower bound is not covered by hardware tests — additional simulation runs compared to Dittus-Boelter trends within 3% but no hardware validation at 18 C. Three additional validation points at 18.0 C inlet are planned (due 23 Aug) but not yet executed. Physics regime (single-phase forced convection, no boiling) consistent throughout. Gap in inlet temperature coverage at lower bound slightly limits achieved level.</t>
+          <t>COU envelope: 0.10–0.14 kg/s, inlet 18–22 C. Validation tests at 0.12 kg/s (nominal) and 0.10 kg/s (lower bound) fully cover the flow range. Inlet temperature tests at 19.5–21.0 C partially cover the 18–22 C range; the 18 C lower bound is assessed by additional simulation runs cross-checked against Dittus-Boelter within 3%. Geometry is identical between model and fixture. Same physics regime (single-phase turbulent forced convection). Residual gap at 18 C inlet to be closed by 3 additional validation points due 23 Aug 2026. Gap acknowledged and bounded.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2960,7 +2851,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>The CHT model is technically sound, traceable, and reproducible. It predicts Tj,max within ~2 C bias (RMSE 2.1 C) and pressure drop within 5.3% of hardware measurements, meeting the pre-defined ±5 C acceptance band at all tested conditions. Code, calculation, and validation evidence are thorough with quantified uncertainties. However, the UQ analysis shows the baseline configuration has a 28% probability of exceeding the 85 C limit under specified input uncertainty distributions. Acceptance is granted with the condition that the subsystem trade adopts a higher-conductivity TIM (≥5 W/m-K, reducing exceedance probability to &lt;5%) or increases minimum flow to 0.13 kg/s before hardware release; these remedies have been analyzed and are within subsystem trades. Three additional validation points at 18.0 C inlet (due 23 Aug 2026) shall be executed to remove residual extrapolation at the lower COU temperature boundary and re-baseline the UQ. Approved by J. Kim, D. Ortega, and S. Patel per the PSB-2 design gate review.</t>
+          <t>The CHT model is technically sound, independently reviewed, and traceable end-to-end. It reproduces validation hardware data within ~2 C RMSE across all sensors, with pressure drop bias of 5.3%, both within pre-defined acceptance bands. A rigorous 200-point LHS UQ propagation with Sobol analysis quantifies output uncertainty. The model is accepted for use at the PSB-2 design gate with two conditions recorded: (1) the higher-k TIM upgrade (to ≥ 5 W/m-K) or minimum flow increase to 0.13 kg/s must be adopted as a design action, because the baseline configuration shows a 28% exceedance probability for the 85 C limit; and (2) three additional validation points at 18.0 C inlet shall be completed by 23 Aug 2026 to remove the residual extrapolation gap at the lower inlet-temperature boundary of the COU envelope.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -2970,7 +2861,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>J. Kim, D. Ortega, S. Patel</t>
+          <t>J. Kim, D. Ortega, S. Patel (TX40 Analysis Advisory Team concurrence 01 Aug 2026)</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
